--- a/rosnedra_forecast/2026/rosnedra_page4.xlsx
+++ b/rosnedra_forecast/2026/rosnedra_page4.xlsx
@@ -416,12 +416,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -443,13 +443,13 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Извлекаемые запасы и природные ресурсы (с указанием категории) (ед.изм)</t>
+          <t>Извлекаемые запасы и прогнозные ресурсы</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -458,21 +458,19 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Южно-Чекурский</t>
+          <t>Летовский</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
           <t>нефть (извл.):
-D1 - 1,247 млн т
-газ (извл.):
-D1 - 0,059 млрд м3</t>
+D0 - 0,138 млн.т</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
@@ -481,21 +479,19 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Западно-Чекурский</t>
+          <t>Мыльниковский</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>нефть (извл.):
-D1 - 0,934 млн т
-газ (извл.):
-D1 - 0,044 млрд м3</t>
+          <t>нефть:
+D1 - 2,2 млн.т</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -504,104 +500,233 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Северо-Чекурский</t>
+          <t>Колыновский</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
           <t>нефть (извл.):
-D1 - 1,563 млн т
-газ (извл.):
-D1 - 0,074 млрд м3</t>
+D1 - 0,3 млн.т,
+D2 - 0,2 млн.т</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Пермский край</t>
+          <t>Республика Башкортостан</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Верхне-Вильвенский</t>
+          <t>Южно-Салаевский</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
           <t>нефть (геол./извл.):
-D1 - 2,417/0,778 млн т
-D1(D3dm) - 201,438/6,043 млн т</t>
+Dл - 2,201/0,927 млн.т
+D1(D3dm) - 34,453/1,034 млн.т</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Пермский край</t>
+          <t>Республика Башкортостан</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Нижне-Вильвенский</t>
+          <t>Куязинский</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>нефть (геол./извл.):
-D1 - 1,885/0,607 млн т
-D1(D3dm) - 166,512/4,995 млн т</t>
+          <t>нефть (извл./геол.):
+D0 - 1,752/0,979 млн.т,
+Dл - 2,2/1,229 млн.т,
+D1 - 1,649/0,644 млн.т,
+D1(D3dm) - 551,115/16,533 млн.т;
+газ (извл./геол.):
+D2 - 0,113/0,113 млрд.м3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Пермский край</t>
+          <t>Республика Башкортостан</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Восточно-Вильвенский</t>
+          <t>Муслюмовский</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>нефть (геол./извл.):
-D1 - 2,774/0,894 млн т
-D1(D3dm) - 238,704/7,161 млн т</t>
+          <t>газ
+C1 - 1,584 млрд.м3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Пермский край</t>
+          <t>Республика Башкортостан</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Северо-Вильвенский</t>
+          <t>Кармаскалинский</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>нефть (геол./извл.):
-D1 - 1,396/0,450 млн т
-газ (геол./извл.):
-D1 - 0,066/0,066 млрд м3</t>
+          <t>нефть (извл.):
+D1 - 0,4 млн.т,
+D2 - 0,3 млн.т</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Кармышевский</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>нефть (извл.):
+D1 - 0,3 млн.т,
+D2 - 0,2 млн.т</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Тюр-Седякский</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>нефть (извл.):
+D0 - 1,671 млн.т</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Рассветовский</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>нефть (извл.):
+D1 - 0,4 млн.т,
+D2 - 0,2 млн.т</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Республика Дагестан</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Наказухский</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>нефть (извл.)
+B1 - 0.003 млн.т</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Республика Дагестан</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Октябрьский</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>нефть (извл.)
+B1 - 0.003 млн.т</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Республика Дагестан</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Манасозень</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>газ (извл.)
+D1 - 0,5 млрд.м3</t>
         </is>
       </c>
     </row>
